--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -439,6 +439,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -481,10 +491,17 @@
     <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>Communication.instantiatesCanonical</t>
@@ -500,6 +517,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -541,7 +561,14 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -567,16 +594,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -673,6 +690,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -751,6 +771,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -803,6 +826,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1070,7 +1096,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1459,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2397,19 +2429,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2421,7 +2453,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2435,10 +2467,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2464,16 +2496,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2510,19 +2542,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2534,7 +2566,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2548,10 +2580,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2574,19 +2606,19 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2635,7 +2667,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2644,27 +2676,27 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2687,15 +2719,17 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2744,7 +2778,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2759,21 +2793,21 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2799,13 +2833,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2855,7 +2889,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2870,25 +2904,25 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2907,16 +2941,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2966,7 +3000,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2975,27 +3009,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3018,13 +3052,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3075,7 +3109,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3096,15 +3130,15 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3133,7 +3167,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>135</v>
@@ -3174,19 +3208,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3198,7 +3232,7 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
@@ -3207,15 +3241,15 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3238,16 +3272,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3297,7 +3331,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3306,7 +3340,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -3323,10 +3357,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3352,13 +3386,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3384,13 +3418,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3408,7 +3442,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3434,10 +3468,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3460,16 +3494,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3519,7 +3553,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3528,7 +3562,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
@@ -3540,15 +3574,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3571,16 +3605,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3630,7 +3664,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3656,14 +3690,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3682,15 +3716,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3739,7 +3775,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3748,27 +3784,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3791,15 +3827,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3848,7 +3886,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3857,10 +3895,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3869,15 +3907,15 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3903,13 +3941,13 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3917,7 +3955,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -3935,31 +3973,31 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -3974,10 +4012,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -3985,14 +4023,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4011,16 +4049,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4046,31 +4084,31 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4079,27 +4117,27 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4122,16 +4160,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4157,13 +4195,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4181,7 +4219,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4190,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4199,18 +4237,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4236,20 +4274,20 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>76</v>
@@ -4270,13 +4308,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4294,7 +4332,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4312,7 +4350,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4320,10 +4358,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4346,15 +4384,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4379,13 +4419,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4403,7 +4443,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4412,7 +4452,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4424,19 +4464,19 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4455,15 +4495,17 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4512,7 +4554,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4521,27 +4563,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4564,16 +4606,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4599,13 +4641,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4623,7 +4665,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4632,7 +4674,7 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4641,18 +4683,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4675,16 +4717,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4734,7 +4776,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4743,27 +4785,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4786,16 +4828,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4845,7 +4887,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4854,27 +4896,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4897,16 +4939,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4956,7 +4998,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4971,10 +5013,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -4982,10 +5024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5008,16 +5050,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5067,7 +5109,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5082,10 +5124,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5093,10 +5135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5119,16 +5161,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5178,7 +5220,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5187,27 +5229,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5230,16 +5272,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5289,7 +5331,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5298,27 +5340,27 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5341,16 +5383,16 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5376,13 +5418,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5400,7 +5442,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5409,27 +5451,27 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5452,15 +5494,17 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5509,7 +5553,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5518,27 +5562,27 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5561,13 +5605,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5618,7 +5662,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5627,7 +5671,7 @@
         <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -5639,15 +5683,15 @@
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5670,13 +5714,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5727,7 +5771,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5748,15 +5792,15 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5785,7 +5829,7 @@
         <v>133</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>135</v>
@@ -5826,19 +5870,19 @@
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5850,7 +5894,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5859,19 +5903,19 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5893,16 +5937,16 @@
         <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -5951,7 +5995,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5963,7 +6007,7 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
@@ -5977,10 +6021,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6003,16 +6047,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6062,7 +6106,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>86</v>
@@ -6071,7 +6115,7 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>98</v>
@@ -6083,15 +6127,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6114,15 +6158,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6171,7 +6217,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6180,19 +6226,19 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>76</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="337">
   <si>
     <t>Property</t>
   </si>
@@ -439,6 +439,136 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Communication.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Communication.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Unique identifier</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Communication.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_Task) &lt;&lt;referenced&gt;&gt;
+</t>
+  </si>
+  <si>
+    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
+  </si>
+  <si>
+    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -447,153 +577,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Communication.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Communication.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Unique identifier</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Communication.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_Task) &lt;&lt;referenced&gt;&gt;
-</t>
-  </si>
-  <si>
-    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
-  </si>
-  <si>
-    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -690,9 +673,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -771,9 +751,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -826,9 +803,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1096,13 +1070,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1427,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2429,19 +2397,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2453,7 +2421,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2467,10 +2435,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2496,16 +2464,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2542,19 +2510,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2566,7 +2534,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2580,10 +2548,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2606,19 +2574,19 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2667,7 +2635,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2676,27 +2644,27 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2719,17 +2687,15 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2778,7 +2744,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2793,21 +2759,21 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2833,13 +2799,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2889,7 +2855,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2904,25 +2870,25 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2941,16 +2907,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3000,7 +2966,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3009,27 +2975,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3052,13 +3018,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3109,7 +3075,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3130,15 +3096,15 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3167,7 +3133,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>135</v>
@@ -3208,19 +3174,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3232,7 +3198,7 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
@@ -3241,15 +3207,15 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3272,16 +3238,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3331,7 +3297,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3340,7 +3306,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -3357,10 +3323,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3386,13 +3352,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3418,13 +3384,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3442,7 +3408,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3468,10 +3434,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3494,16 +3460,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3553,7 +3519,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3562,7 +3528,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
@@ -3574,15 +3540,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3605,16 +3571,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3664,7 +3630,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3690,14 +3656,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3716,17 +3682,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3775,7 +3739,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3784,27 +3748,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3827,17 +3791,15 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3886,7 +3848,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3895,10 +3857,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3907,15 +3869,15 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3941,13 +3903,13 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3955,7 +3917,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -3973,13 +3935,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -3997,7 +3959,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4012,10 +3974,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4023,14 +3985,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4049,16 +4011,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4084,13 +4046,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4108,7 +4070,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4117,27 +4079,27 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4160,16 +4122,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4195,13 +4157,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4219,7 +4181,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4228,7 +4190,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4237,18 +4199,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4274,20 +4236,20 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>76</v>
@@ -4308,13 +4270,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4332,7 +4294,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4350,7 +4312,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4358,10 +4320,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4384,17 +4346,15 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4419,13 +4379,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4443,7 +4403,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4452,7 +4412,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4464,19 +4424,19 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4495,17 +4455,15 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4554,7 +4512,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4563,27 +4521,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4606,16 +4564,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4641,13 +4599,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4665,7 +4623,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4674,7 +4632,7 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4683,18 +4641,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4717,16 +4675,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4776,7 +4734,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4785,27 +4743,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4828,16 +4786,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4887,7 +4845,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4896,27 +4854,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4939,16 +4897,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4998,7 +4956,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5013,10 +4971,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5024,10 +4982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5050,16 +5008,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5109,7 +5067,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5124,10 +5082,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5135,10 +5093,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5161,16 +5119,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5220,7 +5178,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5229,27 +5187,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5272,16 +5230,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5331,7 +5289,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5340,27 +5298,27 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5383,16 +5341,16 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5418,13 +5376,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5442,7 +5400,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5451,27 +5409,27 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5494,17 +5452,15 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5553,7 +5509,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5562,27 +5518,27 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5605,13 +5561,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5662,7 +5618,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5671,7 +5627,7 @@
         <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -5683,15 +5639,15 @@
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5714,13 +5670,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5771,7 +5727,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5792,15 +5748,15 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5829,7 +5785,7 @@
         <v>133</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>135</v>
@@ -5870,19 +5826,19 @@
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5894,7 +5850,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5903,19 +5859,19 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5937,16 +5893,16 @@
         <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -5995,7 +5951,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6007,7 +5963,7 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
@@ -6021,10 +5977,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6047,16 +6003,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6106,7 +6062,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>86</v>
@@ -6115,7 +6071,7 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>98</v>
@@ -6127,15 +6083,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6158,17 +6114,15 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6217,7 +6171,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6226,19 +6180,19 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>346</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
